--- a/data/seeds/Elabscience竞对清单.xlsx
+++ b/data/seeds/Elabscience竞对清单.xlsx
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>诺唯赞 / Vazyme</t>
+          <t>南京诺唯赞生物科技股份有限公司</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>诺唯赞官网</t>
+          <t>https://www.vazyme.com/</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>https://www.4abiotech.com/</t>
+          <t>https://www.4abio.com/</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>https://www.bioassaysystems.com/</t>
+          <t>https://www.bioassaysys.com/</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
